--- a/tests/TC-09/results/teacher_timetables_even.xlsx
+++ b/tests/TC-09/results/teacher_timetables_even.xlsx
@@ -57,14 +57,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-        <bgColor rgb="00BBDEFB"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
   </fills>
@@ -619,37 +619,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -675,23 +660,28 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -756,16 +746,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>CS154
-Room: 101</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+Room: 105</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
@@ -943,37 +948,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 103</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 103</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 103</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 103</t>
-        </is>
-      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 102</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -999,23 +989,28 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 103</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 103</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 104</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 104</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 104</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -1080,16 +1075,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>EC156
 Room: 104</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 104</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 104</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 104</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
@@ -1267,37 +1277,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 104</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -1323,23 +1318,28 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -1404,16 +1404,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>ASD152
-Room: 105</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>

--- a/tests/TC-09/results/teacher_timetables_even.xlsx
+++ b/tests/TC-09/results/teacher_timetables_even.xlsx
@@ -629,17 +629,22 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 105</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -664,24 +669,9 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 105</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 105</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 105</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -695,10 +685,30 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
@@ -720,10 +730,30 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 105</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -747,30 +777,10 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 105</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 105</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 105</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 105</t>
-        </is>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
@@ -958,17 +968,22 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 102</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -993,24 +1008,9 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 104</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 104</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 104</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -1024,10 +1024,30 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
@@ -1049,10 +1069,30 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -1076,30 +1116,10 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 104</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 104</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 104</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 104</t>
-        </is>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
@@ -1287,17 +1307,22 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 104</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -1322,24 +1347,9 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -1353,10 +1363,30 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 103</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 103</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 103</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 103</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
@@ -1378,10 +1408,30 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 103</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 103</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 103</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 103</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -1405,30 +1455,10 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
